--- a/resources/templates/system/container_contract.xlsx
+++ b/resources/templates/system/container_contract.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'HBB340.'!$A$1:$G$66</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -20,13 +20,11 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
   <si>
     <r>
-      <t xml:space="preserve">PROFORM CONTRACT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ssancar LTD. Cho Tae Shin. 499, Aam-dero, Yeonsu-gu, Incheon, Korea  Phone: +82-505-366-9977 Email: ssancar9977@gmail.com</t>
-    </r>
+      <t xml:space="preserve">PROFORMA CONTRACT</t>
+    </r>
+  </si>
+  <si>
+    <t>Ssancar LTD. Cho Tae Shin. 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Korea  Phone: +82-505-355-9977 Email: ssancar9977@gmail.com</t>
   </si>
   <si>
     <r>
@@ -55,7 +53,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -100,7 +98,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -110,7 +108,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -130,7 +128,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -205,22 +203,22 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">SUB TOTAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TOTAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BALANCE MONEY</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BALANCE MONEY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TOTAL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SUB TOTAL</t>
     </r>
   </si>
 </sst>
@@ -1572,28 +1570,35 @@
       <c r="E1" s="44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM CONTRACT</t>
+            <t xml:space="preserve">PROFORMA CONTRACT</t>
           </r>
         </is>
       </c>
       <c r="F1" s="54"/>
       <c r="G1" s="55"/>
       <c r="H1" s="12"/>
+      <c r="I1" s="53"/>
       <c r="J1" s="53"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="45" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Ssancar LTD. Cho Tae Shin. 499, Aam-dero, Yeonsu-gu, Incheon, Korea  Phone: +82-505-366-9977 Email: ssancar9977@gmail.com</t>
-          </r>
-        </is>
-      </c>
+      <c r="A2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="4"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
       <c r="A3" s="56"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="9" t="inlineStr">
         <is>
           <r>
@@ -1601,11 +1606,13 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="46" t="str">
         <f>TODAY()</f>
-        <v>46166</v>
+        <v>0</v>
       </c>
       <c r="G3" s="57"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
       <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
@@ -1628,10 +1635,15 @@
         </is>
       </c>
       <c r="G4" s="58"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
       <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
       <c r="A5" s="31"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <r>
@@ -1647,23 +1659,33 @@
         </is>
       </c>
       <c r="G5" s="58"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
       <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
       <c r="A6" s="31"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="58"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
       <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
       <c r="A7" s="31"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <r>
@@ -1673,17 +1695,26 @@
       </c>
       <c r="F7" s="33"/>
       <c r="G7" s="58"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
       <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
       <c r="A8" s="31"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="9"/>
       <c r="F8" s="33"/>
       <c r="G8" s="58"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
       <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A9" s="31"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="7"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -1700,6 +1731,8 @@
         </is>
       </c>
       <c r="G9" s="58"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
       <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
@@ -1716,6 +1749,8 @@
       <c r="E10" s="59"/>
       <c r="F10" s="59"/>
       <c r="G10" s="60"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
       <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
@@ -1750,13 +1785,15 @@
         </is>
       </c>
       <c r="G11" s="61"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
       <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A12" s="37" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -1772,7 +1809,7 @@
       <c r="E12" s="38" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -1784,6 +1821,8 @@
         </is>
       </c>
       <c r="G12" s="63"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
       <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
@@ -1806,19 +1845,26 @@
       <c r="E13" s="41" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
       <c r="F13" s="66"/>
       <c r="G13" s="67"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
       <c r="J13" s="53"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="13.5" s="53" customFormat="1">
       <c r="A14" s="8"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="7"/>
       <c r="E14" s="68"/>
+      <c r="F14" s="53"/>
       <c r="G14" s="21"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
       <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
@@ -1871,12 +1917,14 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
       <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A16" s="6" t="str">
         <f>RIGHT(E16,6)</f>
-        <v>281238</v>
+        <v>0</v>
       </c>
       <c r="B16" s="50" t="inlineStr">
         <is>
@@ -1908,16 +1956,17 @@
       <c r="G16" s="70">
         <v>1075</v>
       </c>
-      <c r="I16" s="28">
+      <c r="H16" s="53"/>
+      <c r="I16" s="28" t="str">
         <f>F16+G16</f>
-        <v>3375</v>
+        <v>0</v>
       </c>
       <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A17" s="6" t="str">
         <f>RIGHT(E17,6)</f>
-        <v>886217</v>
+        <v>0</v>
       </c>
       <c r="B17" s="50" t="inlineStr">
         <is>
@@ -1949,16 +1998,17 @@
       <c r="G17" s="70">
         <v>1075</v>
       </c>
-      <c r="I17" s="28">
+      <c r="H17" s="53"/>
+      <c r="I17" s="28" t="str">
         <f>F17+G17</f>
-        <v>7475</v>
+        <v>0</v>
       </c>
       <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A18" s="6" t="str">
         <f>RIGHT(E18,6)</f>
-        <v>680072</v>
+        <v>0</v>
       </c>
       <c r="B18" s="50" t="inlineStr">
         <is>
@@ -1990,16 +2040,17 @@
       <c r="G18" s="70">
         <v>1075</v>
       </c>
-      <c r="I18" s="28">
+      <c r="H18" s="53"/>
+      <c r="I18" s="28" t="str">
         <f>F18+G18</f>
-        <v>6175</v>
+        <v>0</v>
       </c>
       <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A19" s="6" t="str">
         <f>RIGHT(E19,6)</f>
-        <v>687864</v>
+        <v>0</v>
       </c>
       <c r="B19" s="50" t="inlineStr">
         <is>
@@ -2031,16 +2082,17 @@
       <c r="G19" s="70">
         <v>1075</v>
       </c>
-      <c r="I19" s="28">
+      <c r="H19" s="53"/>
+      <c r="I19" s="28" t="str">
         <f>F19+G19</f>
-        <v>2675</v>
+        <v>0</v>
       </c>
       <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A20" s="6" t="str">
         <f>RIGHT(E20,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2048,7 +2100,8 @@
       <c r="E20" s="5"/>
       <c r="F20" s="71"/>
       <c r="G20" s="72"/>
-      <c r="I20" s="28">
+      <c r="H20" s="53"/>
+      <c r="I20" s="28" t="str">
         <f>F20+G20</f>
         <v>0</v>
       </c>
@@ -2057,7 +2110,7 @@
     <row r="21" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A21" s="6" t="str">
         <f>RIGHT(E21,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2065,7 +2118,8 @@
       <c r="E21" s="5"/>
       <c r="F21" s="71"/>
       <c r="G21" s="72"/>
-      <c r="I21" s="28">
+      <c r="H21" s="53"/>
+      <c r="I21" s="28" t="str">
         <f>F21+G21</f>
         <v>0</v>
       </c>
@@ -2074,7 +2128,7 @@
     <row r="22" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A22" s="6" t="str">
         <f>RIGHT(E22,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2082,7 +2136,8 @@
       <c r="E22" s="5"/>
       <c r="F22" s="71"/>
       <c r="G22" s="72"/>
-      <c r="I22" s="28">
+      <c r="H22" s="53"/>
+      <c r="I22" s="28" t="str">
         <f>F22+G22</f>
         <v>0</v>
       </c>
@@ -2091,7 +2146,7 @@
     <row r="23" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A23" s="6" t="str">
         <f>RIGHT(E23,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2099,7 +2154,8 @@
       <c r="E23" s="5"/>
       <c r="F23" s="71"/>
       <c r="G23" s="72"/>
-      <c r="I23" s="28">
+      <c r="H23" s="53"/>
+      <c r="I23" s="28" t="str">
         <f>F23+G23</f>
         <v>0</v>
       </c>
@@ -2108,7 +2164,7 @@
     <row r="24" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A24" s="6" t="str">
         <f>RIGHT(E24,6)</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2122,7 +2178,8 @@
       </c>
       <c r="F24" s="71"/>
       <c r="G24" s="72"/>
-      <c r="I24" s="28">
+      <c r="H24" s="53"/>
+      <c r="I24" s="28" t="str">
         <f>F24+G24</f>
         <v>0</v>
       </c>
@@ -2131,7 +2188,7 @@
     <row r="25" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A25" s="6" t="str">
         <f>RIGHT(E25,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2139,7 +2196,8 @@
       <c r="E25" s="5"/>
       <c r="F25" s="71"/>
       <c r="G25" s="72"/>
-      <c r="I25" s="28">
+      <c r="H25" s="53"/>
+      <c r="I25" s="28" t="str">
         <f>F25+G25</f>
         <v>0</v>
       </c>
@@ -2148,7 +2206,7 @@
     <row r="26" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A26" s="6" t="str">
         <f>RIGHT(E26,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -2157,7 +2215,7 @@
       <c r="F26" s="73"/>
       <c r="G26" s="74"/>
       <c r="H26" s="53"/>
-      <c r="I26" s="28">
+      <c r="I26" s="28" t="str">
         <f>F26+G26</f>
         <v>0</v>
       </c>
@@ -2166,7 +2224,7 @@
     <row r="27" spans="1:10" customHeight="1" ht="20.1">
       <c r="A27" s="6" t="str">
         <f>RIGHT(E27,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -2175,7 +2233,7 @@
       <c r="F27" s="73"/>
       <c r="G27" s="74"/>
       <c r="H27" s="53"/>
-      <c r="I27" s="28">
+      <c r="I27" s="28" t="str">
         <f>F27+G27</f>
         <v>0</v>
       </c>
@@ -2184,7 +2242,7 @@
     <row r="28" spans="1:10" customHeight="1" ht="20.1">
       <c r="A28" s="6" t="str">
         <f>RIGHT(E28,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -2193,7 +2251,7 @@
       <c r="F28" s="73"/>
       <c r="G28" s="74"/>
       <c r="H28" s="53"/>
-      <c r="I28" s="28">
+      <c r="I28" s="28" t="str">
         <f>F28+G28</f>
         <v>0</v>
       </c>
@@ -2202,7 +2260,7 @@
     <row r="29" spans="1:10" customHeight="1" ht="20.1">
       <c r="A29" s="6" t="str">
         <f>RIGHT(E29,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -2211,7 +2269,7 @@
       <c r="F29" s="73"/>
       <c r="G29" s="74"/>
       <c r="H29" s="53"/>
-      <c r="I29" s="28">
+      <c r="I29" s="28" t="str">
         <f>F29+G29</f>
         <v>0</v>
       </c>
@@ -2220,7 +2278,7 @@
     <row r="30" spans="1:10" customHeight="1" ht="20.1">
       <c r="A30" s="6" t="str">
         <f>RIGHT(E30,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -2229,7 +2287,7 @@
       <c r="F30" s="73"/>
       <c r="G30" s="74"/>
       <c r="H30" s="53"/>
-      <c r="I30" s="28">
+      <c r="I30" s="28" t="str">
         <f>F30+G30</f>
         <v>0</v>
       </c>
@@ -2238,7 +2296,7 @@
     <row r="31" spans="1:10" customHeight="1" ht="20.1">
       <c r="A31" s="6" t="str">
         <f>RIGHT(E31,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -2247,7 +2305,7 @@
       <c r="F31" s="73"/>
       <c r="G31" s="74"/>
       <c r="H31" s="53"/>
-      <c r="I31" s="28">
+      <c r="I31" s="28" t="str">
         <f>F31+G31</f>
         <v>0</v>
       </c>
@@ -2256,7 +2314,7 @@
     <row r="32" spans="1:10" customHeight="1" ht="20.1">
       <c r="A32" s="6" t="str">
         <f>RIGHT(E32,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -2265,7 +2323,7 @@
       <c r="F32" s="73"/>
       <c r="G32" s="74"/>
       <c r="H32" s="53"/>
-      <c r="I32" s="28">
+      <c r="I32" s="28" t="str">
         <f>F32+G32</f>
         <v>0</v>
       </c>
@@ -2274,7 +2332,7 @@
     <row r="33" spans="1:10" customHeight="1" ht="20.1">
       <c r="A33" s="6" t="str">
         <f>RIGHT(E33,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -2283,7 +2341,7 @@
       <c r="F33" s="73"/>
       <c r="G33" s="74"/>
       <c r="H33" s="53"/>
-      <c r="I33" s="28">
+      <c r="I33" s="28" t="str">
         <f>F33+G33</f>
         <v>0</v>
       </c>
@@ -2292,7 +2350,7 @@
     <row r="34" spans="1:10" customHeight="1" ht="20.1">
       <c r="A34" s="6" t="str">
         <f>RIGHT(E34,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -2301,7 +2359,7 @@
       <c r="F34" s="73"/>
       <c r="G34" s="74"/>
       <c r="H34" s="53"/>
-      <c r="I34" s="28">
+      <c r="I34" s="28" t="str">
         <f>F34+G34</f>
         <v>0</v>
       </c>
@@ -2310,7 +2368,7 @@
     <row r="35" spans="1:10" customHeight="1" ht="20.1">
       <c r="A35" s="6" t="str">
         <f>RIGHT(E35,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -2319,7 +2377,7 @@
       <c r="F35" s="73"/>
       <c r="G35" s="74"/>
       <c r="H35" s="53"/>
-      <c r="I35" s="28">
+      <c r="I35" s="28" t="str">
         <f>F35+G35</f>
         <v>0</v>
       </c>
@@ -2328,7 +2386,7 @@
     <row r="36" spans="1:10" customHeight="1" ht="20.1">
       <c r="A36" s="6" t="str">
         <f>RIGHT(E36,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -2337,7 +2395,7 @@
       <c r="F36" s="73"/>
       <c r="G36" s="74"/>
       <c r="H36" s="53"/>
-      <c r="I36" s="28">
+      <c r="I36" s="28" t="str">
         <f>F36+G36</f>
         <v>0</v>
       </c>
@@ -2346,7 +2404,7 @@
     <row r="37" spans="1:10" customHeight="1" ht="20.1">
       <c r="A37" s="6" t="str">
         <f>RIGHT(E37,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -2355,7 +2413,7 @@
       <c r="F37" s="73"/>
       <c r="G37" s="74"/>
       <c r="H37" s="53"/>
-      <c r="I37" s="28">
+      <c r="I37" s="28" t="str">
         <f>F37+G37</f>
         <v>0</v>
       </c>
@@ -2364,7 +2422,7 @@
     <row r="38" spans="1:10" customHeight="1" ht="20.1">
       <c r="A38" s="6" t="str">
         <f>RIGHT(E38,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -2373,7 +2431,7 @@
       <c r="F38" s="73"/>
       <c r="G38" s="74"/>
       <c r="H38" s="53"/>
-      <c r="I38" s="28">
+      <c r="I38" s="28" t="str">
         <f>F38+G38</f>
         <v>0</v>
       </c>
@@ -2382,7 +2440,7 @@
     <row r="39" spans="1:10" customHeight="1" ht="20.1">
       <c r="A39" s="6" t="str">
         <f>RIGHT(E39,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -2391,7 +2449,7 @@
       <c r="F39" s="73"/>
       <c r="G39" s="74"/>
       <c r="H39" s="53"/>
-      <c r="I39" s="28">
+      <c r="I39" s="28" t="str">
         <f>F39+G39</f>
         <v>0</v>
       </c>
@@ -2400,7 +2458,7 @@
     <row r="40" spans="1:10" customHeight="1" ht="20.1">
       <c r="A40" s="6" t="str">
         <f>RIGHT(E40,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -2409,7 +2467,7 @@
       <c r="F40" s="73"/>
       <c r="G40" s="74"/>
       <c r="H40" s="53"/>
-      <c r="I40" s="28">
+      <c r="I40" s="28" t="str">
         <f>F40+G40</f>
         <v>0</v>
       </c>
@@ -2418,7 +2476,7 @@
     <row r="41" spans="1:10" customHeight="1" ht="20.1">
       <c r="A41" s="6" t="str">
         <f>RIGHT(E41,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -2427,7 +2485,7 @@
       <c r="F41" s="73"/>
       <c r="G41" s="74"/>
       <c r="H41" s="53"/>
-      <c r="I41" s="28">
+      <c r="I41" s="28" t="str">
         <f>F41+G41</f>
         <v>0</v>
       </c>
@@ -2436,7 +2494,7 @@
     <row r="42" spans="1:10" customHeight="1" ht="20.1">
       <c r="A42" s="6" t="str">
         <f>RIGHT(E42,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -2445,7 +2503,7 @@
       <c r="F42" s="73"/>
       <c r="G42" s="74"/>
       <c r="H42" s="53"/>
-      <c r="I42" s="28">
+      <c r="I42" s="28" t="str">
         <f>F42+G42</f>
         <v>0</v>
       </c>
@@ -2454,7 +2512,7 @@
     <row r="43" spans="1:10" customHeight="1" ht="20.1">
       <c r="A43" s="6" t="str">
         <f>RIGHT(E43,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -2463,7 +2521,7 @@
       <c r="F43" s="73"/>
       <c r="G43" s="74"/>
       <c r="H43" s="53"/>
-      <c r="I43" s="28">
+      <c r="I43" s="28" t="str">
         <f>F43+G43</f>
         <v>0</v>
       </c>
@@ -2472,7 +2530,7 @@
     <row r="44" spans="1:10" customHeight="1" ht="20.1">
       <c r="A44" s="6" t="str">
         <f>RIGHT(E44,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -2481,7 +2539,7 @@
       <c r="F44" s="73"/>
       <c r="G44" s="74"/>
       <c r="H44" s="53"/>
-      <c r="I44" s="28">
+      <c r="I44" s="28" t="str">
         <f>F44+G44</f>
         <v>0</v>
       </c>
@@ -2490,7 +2548,7 @@
     <row r="45" spans="1:10" customHeight="1" ht="20.1">
       <c r="A45" s="6" t="str">
         <f>RIGHT(E45,6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -2499,7 +2557,7 @@
       <c r="F45" s="73"/>
       <c r="G45" s="74"/>
       <c r="H45" s="53"/>
-      <c r="I45" s="28">
+      <c r="I45" s="28" t="str">
         <f>F45+G45</f>
         <v>0</v>
       </c>
@@ -2517,14 +2575,15 @@
           </r>
         </is>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="35" t="str">
         <f>SUM(F16:G45)</f>
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="G46" s="76"/>
-      <c r="I46" s="28">
+      <c r="H46" s="53"/>
+      <c r="I46" s="28" t="str">
         <f>SUM(F16:F45)</f>
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
@@ -2554,9 +2613,10 @@
         </is>
       </c>
       <c r="G47" s="76"/>
-      <c r="I47" s="28">
+      <c r="H47" s="53"/>
+      <c r="I47" s="28" t="str">
         <f>SUM(G16:G45)</f>
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
@@ -2580,6 +2640,8 @@
         </is>
       </c>
       <c r="G48" s="76"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
       <c r="J48" s="53"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2590,6 +2652,8 @@
       <c r="E49" s="23"/>
       <c r="F49" s="77"/>
       <c r="G49" s="61"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
       <c r="J49" s="53"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2600,6 +2664,8 @@
       <c r="E50" s="23"/>
       <c r="F50" s="77"/>
       <c r="G50" s="61"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
       <c r="J50" s="53"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2610,6 +2676,8 @@
       <c r="E51" s="24"/>
       <c r="F51" s="77"/>
       <c r="G51" s="61"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
       <c r="J51" s="53"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
@@ -2624,11 +2692,13 @@
           </r>
         </is>
       </c>
-      <c r="F52" s="35">
+      <c r="F52" s="35" t="str">
         <f>SUM(F46:G51)</f>
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="G52" s="76"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
       <c r="J52" s="53"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2651,6 +2721,8 @@
       </c>
       <c r="F53" s="78"/>
       <c r="G53" s="76"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
       <c r="J53" s="53"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2661,6 +2733,8 @@
       <c r="E54" s="26"/>
       <c r="F54" s="78"/>
       <c r="G54" s="76"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
       <c r="J54" s="53"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2671,6 +2745,8 @@
       <c r="E55" s="26"/>
       <c r="F55" s="78"/>
       <c r="G55" s="76"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
       <c r="J55" s="53"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2681,6 +2757,8 @@
       <c r="E56" s="26"/>
       <c r="F56" s="78"/>
       <c r="G56" s="76"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
       <c r="J56" s="53"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15.95" s="53" customFormat="1">
@@ -2691,6 +2769,8 @@
       <c r="E57" s="26"/>
       <c r="F57" s="78"/>
       <c r="G57" s="76"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
       <c r="J57" s="53"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="24.95" s="53" customFormat="1">
@@ -2705,16 +2785,21 @@
           </r>
         </is>
       </c>
-      <c r="F58" s="30">
+      <c r="F58" s="30" t="str">
         <f>SUM(F52-F53-F54-F55-F56-F57)</f>
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="G58" s="79"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
       <c r="J58" s="53"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A59" s="31"/>
       <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
       <c r="F59" s="32" t="inlineStr">
         <is>
           <r>
@@ -2723,26 +2808,56 @@
         </is>
       </c>
       <c r="G59" s="4"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
       <c r="J59" s="53"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A60" s="31"/>
+      <c r="B60" s="53"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
       <c r="G60" s="4"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
       <c r="J60" s="53"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A61" s="31"/>
+      <c r="B61" s="53"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
       <c r="G61" s="4"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
       <c r="J61" s="53"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A62" s="31"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
       <c r="G62" s="4"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
       <c r="J62" s="53"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
       <c r="A63" s="31"/>
+      <c r="B63" s="53"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
       <c r="G63" s="4"/>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
       <c r="J63" s="53"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="20.1" s="53" customFormat="1">
@@ -2753,6 +2868,8 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
       <c r="J64" s="53"/>
     </row>
   </sheetData>
